--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -769,11 +769,11 @@
         <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03943586691977972</v>
+        <v>0.03974912559381315</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1062,11 +1062,11 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02670984607512285</v>
+        <v>0.02692201564609109</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1355,11 +1355,11 @@
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03344279896386573</v>
+        <v>0.03370845172308358</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1648,11 +1648,11 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03677228116159573</v>
+        <v>0.03706438165126667</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1941,11 +1941,11 @@
         <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>0.04646477378165416</v>
+        <v>0.04683386655331082</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2234,11 +2234,11 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05830293270691637</v>
+        <v>0.05876606185351739</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2527,11 +2527,11 @@
         <v>8</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04631679679508838</v>
+        <v>0.04668471411205823</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2820,11 +2820,11 @@
         <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>0.02500811072961641</v>
+        <v>0.02520676257168639</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3113,11 +3113,11 @@
         <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>0.07043704560531013</v>
+        <v>0.07099656203622912</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3406,11 +3406,11 @@
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.07043704560531013</v>
+        <v>0.07099656203622912</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3699,11 +3699,11 @@
         <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1685457876984207</v>
+        <v>0.1698846305866911</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3992,11 +3992,11 @@
         <v>33</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1489388369784551</v>
+        <v>0.150121932120724</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4285,11 +4285,11 @@
         <v>17</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0795441625751913</v>
+        <v>0.0801980491565122</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4578,11 +4578,11 @@
         <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>0.04050723990659003</v>
+        <v>0.04084022651131074</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4871,11 +4871,11 @@
         <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0447711598967574</v>
+        <v>0.04513919772302766</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5164,11 +5164,11 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0459474136871484</v>
+        <v>0.04632512081591509</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5457,11 +5457,11 @@
         <v>9</v>
       </c>
       <c r="R34" t="n">
-        <v>0.06506153778100213</v>
+        <v>0.06559637107533577</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5750,11 +5750,11 @@
         <v>9</v>
       </c>
       <c r="R36" t="n">
-        <v>0.06785514053318076</v>
+        <v>0.0684129384209434</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -6043,11 +6043,11 @@
         <v>8</v>
       </c>
       <c r="R38" t="n">
-        <v>0.04925562747262308</v>
+        <v>0.04966052951466098</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6336,11 +6336,11 @@
         <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>0.03117072544536147</v>
+        <v>0.03142696196151679</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6629,11 +6629,11 @@
         <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>0.02764196407418848</v>
+        <v>0.02786919268285451</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6922,11 +6922,11 @@
         <v>11</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0705017115615605</v>
+        <v>0.07108126537994011</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7215,11 +7215,11 @@
         <v>19</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1667339747879241</v>
+        <v>0.1681045984167926</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7508,11 +7508,11 @@
         <v>31</v>
       </c>
       <c r="R48" t="n">
-        <v>0.1434294465658024</v>
+        <v>0.1446084971389605</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7801,11 +7801,11 @@
         <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>0.08141533501989227</v>
+        <v>0.08203234207854505</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8094,11 +8094,11 @@
         <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>0.05585895182979156</v>
+        <v>0.05628227954267889</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8387,11 +8387,11 @@
         <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>0.05790346248499962</v>
+        <v>0.05834228454554818</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8680,11 +8680,11 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.05644309773127958</v>
+        <v>0.05687085240064155</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8973,11 +8973,11 @@
         <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>0.06914827108864394</v>
+        <v>0.06967231206132929</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9266,11 +9266,11 @@
         <v>6</v>
       </c>
       <c r="R60" t="n">
-        <v>0.07623104014418614</v>
+        <v>0.07680875796412649</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9559,11 +9559,11 @@
         <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>0.05585895182979156</v>
+        <v>0.05628227954267889</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9852,11 +9852,11 @@
         <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>0.03263915224564291</v>
+        <v>0.03288650843866335</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10145,11 +10145,11 @@
         <v>150</v>
       </c>
       <c r="R66" t="n">
-        <v>0.02884220388597081</v>
+        <v>0.02906078486190609</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10882,11 +10882,11 @@
         <v>10</v>
       </c>
       <c r="R71" t="n">
-        <v>0.09463163604105865</v>
+        <v>0.09534880298995012</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11767,11 +11767,11 @@
         <v>25</v>
       </c>
       <c r="R77" t="n">
-        <v>0.2190547130580061</v>
+        <v>0.2207148217359956</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12800,11 +12800,11 @@
         <v>24</v>
       </c>
       <c r="R84" t="n">
-        <v>0.1882410167545133</v>
+        <v>0.1896676034784656</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13685,11 +13685,11 @@
         <v>22</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1042053387505249</v>
+        <v>0.1051007123736524</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14570,11 +14570,11 @@
         <v>22</v>
       </c>
       <c r="R96" t="n">
-        <v>0.06149347756467994</v>
+        <v>0.06202185392683176</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15455,11 +15455,11 @@
         <v>7</v>
       </c>
       <c r="R102" t="n">
-        <v>0.07237086156786626</v>
+        <v>0.07299270072992702</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16488,11 +16488,11 @@
         <v>8</v>
       </c>
       <c r="R109" t="n">
-        <v>0.07838968071629601</v>
+        <v>0.07906323596097303</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17373,11 +17373,11 @@
         <v>7</v>
       </c>
       <c r="R115" t="n">
-        <v>0.09557594744133038</v>
+        <v>0.09639717390986352</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18406,11 +18406,11 @@
         <v>8</v>
       </c>
       <c r="R122" t="n">
-        <v>0.09137002562676501</v>
+        <v>0.09215511314600003</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19291,11 +19291,11 @@
         <v>7</v>
       </c>
       <c r="R128" t="n">
-        <v>0.07418375890173064</v>
+        <v>0.07482117519710955</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20176,11 +20176,11 @@
         <v>2</v>
       </c>
       <c r="R134" t="n">
-        <v>0.04292940886590864</v>
+        <v>0.04329827538288256</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -21209,11 +21209,11 @@
         <v>7</v>
       </c>
       <c r="R141" t="n">
-        <v>0.07418375890173064</v>
+        <v>0.07482117519710955</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -22094,11 +22094,11 @@
         <v>14</v>
       </c>
       <c r="R147" t="n">
-        <v>0.08237805485079766</v>
+        <v>0.08308587978877463</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -22979,11 +22979,11 @@
         <v>23</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1313262828651361</v>
+        <v>0.1324546904027032</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -24012,11 +24012,11 @@
         <v>12</v>
       </c>
       <c r="R160" t="n">
-        <v>0.1121820870195281</v>
+        <v>0.1131460000292556</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -24897,11 +24897,11 @@
         <v>15</v>
       </c>
       <c r="R166" t="n">
-        <v>0.07723610194200581</v>
+        <v>0.07788094096450315</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -25930,11 +25930,11 @@
         <v>3</v>
       </c>
       <c r="R173" t="n">
-        <v>0.06311457584066893</v>
+        <v>0.0636415151911425</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -26815,11 +26815,11 @@
         <v>4</v>
       </c>
       <c r="R179" t="n">
-        <v>0.07262499137830397</v>
+        <v>0.07323133254871192</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -27700,11 +27700,11 @@
         <v>3</v>
       </c>
       <c r="R185" t="n">
-        <v>0.07262499137830397</v>
+        <v>0.07323133254871192</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -28585,11 +28585,11 @@
         <v>7</v>
       </c>
       <c r="R191" t="n">
-        <v>0.07968575442897242</v>
+        <v>0.08035104543539223</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -29618,11 +29618,11 @@
         <v>5</v>
       </c>
       <c r="R198" t="n">
-        <v>0.07889321980083616</v>
+        <v>0.07955189398892812</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -30503,11 +30503,11 @@
         <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0.06023263173835528</v>
+        <v>0.06073550993127297</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -31388,11 +31388,11 @@
         <v>2</v>
       </c>
       <c r="R210" t="n">
-        <v>0.03897829398379211</v>
+        <v>0.03930372113973526</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -32421,11 +32421,11 @@
         <v>9</v>
       </c>
       <c r="R217" t="n">
-        <v>0.03919443979146563</v>
+        <v>0.03952167153422548</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -33306,11 +33306,11 @@
         <v>8</v>
       </c>
       <c r="R223" t="n">
-        <v>0.06556422832763553</v>
+        <v>0.06611161966203159</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -34339,11 +34339,11 @@
         <v>18</v>
       </c>
       <c r="R230" t="n">
-        <v>0.1256527628608752</v>
+        <v>0.1267018293303111</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -35224,11 +35224,11 @@
         <v>10</v>
       </c>
       <c r="R236" t="n">
-        <v>0.1047586681191012</v>
+        <v>0.1056332911962571</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">

--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1214,6 +1229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1507,6 +1532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1655,6 +1685,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1800,6 +1835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1948,6 +1988,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2093,6 +2138,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2241,6 +2291,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2386,6 +2441,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2534,6 +2594,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2679,6 +2744,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2827,6 +2897,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2972,6 +3047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3120,6 +3200,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3265,6 +3350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3413,6 +3503,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3558,6 +3653,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3706,6 +3806,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3851,6 +3956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3999,6 +4109,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4144,6 +4259,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4292,6 +4412,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4437,6 +4562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4585,6 +4715,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4730,6 +4865,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4878,6 +5018,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5023,6 +5168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5171,6 +5321,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5316,6 +5471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5464,6 +5624,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5609,6 +5774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5757,6 +5927,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5902,6 +6077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6050,6 +6230,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6195,6 +6380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6343,6 +6533,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6488,6 +6683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6636,6 +6836,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6781,6 +6986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6929,6 +7139,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7074,6 +7289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7222,6 +7442,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7367,6 +7592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7515,6 +7745,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7660,6 +7895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7808,6 +8048,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7953,6 +8198,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8101,6 +8351,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8246,6 +8501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8394,6 +8654,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8539,6 +8804,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8687,6 +8957,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8832,6 +9107,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8980,6 +9260,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9125,6 +9410,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9273,6 +9563,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9418,6 +9713,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9566,6 +9866,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9711,6 +10016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9859,6 +10169,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10004,6 +10319,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10152,6 +10472,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10297,6 +10622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10889,6 +11219,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11034,6 +11369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11774,6 +12114,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11919,6 +12264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12807,6 +13157,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12952,6 +13307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13692,6 +14052,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13837,6 +14202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14577,6 +14947,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14870,6 +15245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15462,6 +15842,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15755,6 +16140,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16495,6 +16885,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16640,6 +17035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17380,6 +17780,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17525,6 +17930,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18413,6 +18823,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18558,6 +18973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19298,6 +19718,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19443,6 +19868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20183,6 +20613,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20328,6 +20763,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21216,6 +21656,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21361,6 +21806,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22101,6 +22551,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22246,6 +22701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22986,6 +23446,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23279,6 +23744,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24019,6 +24489,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24164,6 +24639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24904,6 +25384,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25049,6 +25534,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25937,6 +26427,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26082,6 +26577,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26822,6 +27322,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26967,6 +27472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27707,6 +28217,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27852,6 +28367,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28592,6 +29112,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28737,6 +29262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29625,6 +30155,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29770,6 +30305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30510,6 +31050,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30655,6 +31200,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31395,6 +31945,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31688,6 +32243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32428,6 +32988,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32573,6 +33138,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33313,6 +33883,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33458,6 +34033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34346,6 +34926,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34491,6 +35076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35231,6 +35821,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35374,6 +35969,11 @@
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">

--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -10775,28 +10775,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -10923,28 +10937,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -11071,28 +11099,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -11522,28 +11564,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11670,28 +11726,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -11818,28 +11888,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -11966,28 +12050,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -12417,28 +12515,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12565,28 +12677,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12713,28 +12839,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -12861,28 +13001,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -13009,28 +13163,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -13460,28 +13628,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -13608,28 +13790,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13756,28 +13952,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13904,28 +14114,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -14355,28 +14579,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14503,28 +14741,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14651,28 +14903,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14799,28 +15065,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -15100,28 +15380,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -15398,28 +15692,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15546,28 +15854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15694,28 +16016,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -15995,28 +16331,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -16293,28 +16643,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -16441,28 +16805,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -16589,28 +16967,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16737,28 +17129,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -17188,28 +17594,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17336,28 +17756,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -17484,28 +17918,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -17632,28 +18080,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -18083,28 +18545,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -18231,28 +18707,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -18379,28 +18869,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18527,28 +19031,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -18675,28 +19193,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -19126,28 +19658,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -19274,28 +19820,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -19422,28 +19982,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -19570,28 +20144,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -20021,28 +20609,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20169,28 +20771,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20317,28 +20933,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -20465,28 +21095,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -20916,28 +21560,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -21064,28 +21722,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21212,28 +21884,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -21360,28 +22046,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -21508,28 +22208,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -21959,28 +22673,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -22107,28 +22835,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -22255,28 +22997,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -22403,28 +23159,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22854,28 +23624,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -23002,28 +23786,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -23150,28 +23948,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -23298,28 +24110,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -23599,28 +24425,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -23897,28 +24737,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -24045,28 +24899,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -24193,28 +25061,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -24341,28 +25223,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -24792,28 +25688,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -24940,28 +25850,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -25088,28 +26012,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -25236,28 +26174,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -25687,28 +26639,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -25835,28 +26801,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -25983,28 +26963,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -26131,28 +27125,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -26279,28 +27287,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -26730,28 +27752,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -26878,28 +27914,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -27026,28 +28076,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -27174,28 +28238,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -27625,28 +28703,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -27773,28 +28865,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -27921,28 +29027,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -28069,28 +29189,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -28520,28 +29654,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -28668,28 +29816,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -28816,28 +29978,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -28964,28 +30140,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -29415,28 +30605,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
@@ -29563,28 +30767,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -29711,28 +30929,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -29859,28 +31091,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -30007,28 +31253,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -30458,28 +31718,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -30606,28 +31880,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -30754,28 +32042,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -30902,28 +32204,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -31353,28 +32669,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -31501,28 +32831,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -31649,28 +32993,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -31797,28 +33155,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -32098,28 +33470,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -32396,28 +33782,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -32544,28 +33944,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -32692,28 +34106,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -32840,28 +34268,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -33291,28 +34733,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -33439,28 +34895,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -33587,28 +35057,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -33735,28 +35219,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -34186,28 +35684,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -34334,28 +35846,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -34482,28 +36008,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -34630,28 +36170,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -34778,28 +36332,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -35229,28 +36797,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -35377,28 +36959,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -35525,28 +37121,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -35673,28 +37283,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -36124,28 +37748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -36272,28 +37910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -36420,28 +38072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -36568,28 +38234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">

--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.03974912559381315</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0.0328075025427096</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1074,11 +1044,6 @@
       <c r="R4" t="n">
         <v>0.02692201564609109</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1091,22 +1056,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1224,11 +1179,6 @@
       <c r="R5" t="n">
         <v>0.02255515799811285</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1241,22 +1191,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,11 +1317,6 @@
       <c r="R6" t="n">
         <v>0.03370845172308358</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1394,22 +1329,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1527,11 +1452,6 @@
       <c r="R7" t="n">
         <v>0.0205046890891935</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1544,22 +1464,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1680,11 +1590,6 @@
       <c r="R8" t="n">
         <v>0.03706438165126667</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1697,22 +1602,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1830,11 +1725,6 @@
       <c r="R9" t="n">
         <v>0.03075703363379025</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1847,22 +1737,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1983,11 +1863,6 @@
       <c r="R10" t="n">
         <v>0.04683386655331082</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2000,22 +1875,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2133,11 +1998,6 @@
       <c r="R11" t="n">
         <v>0.0328075025427096</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2150,22 +2010,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2286,11 +2136,6 @@
       <c r="R12" t="n">
         <v>0.05876606185351739</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2303,22 +2148,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2436,11 +2271,6 @@
       <c r="R13" t="n">
         <v>0.0451103159962257</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2453,22 +2283,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2589,11 +2409,6 @@
       <c r="R14" t="n">
         <v>0.04668471411205823</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2606,22 +2421,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2739,11 +2544,6 @@
       <c r="R15" t="n">
         <v>0.0492112538140644</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2756,22 +2556,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2892,11 +2682,6 @@
       <c r="R16" t="n">
         <v>0.02520676257168639</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2909,22 +2694,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3042,11 +2817,6 @@
       <c r="R17" t="n">
         <v>0.041009378178387</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3059,22 +2829,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3195,11 +2955,6 @@
       <c r="R18" t="n">
         <v>0.07099656203622912</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3212,22 +2967,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3345,11 +3090,6 @@
       <c r="R19" t="n">
         <v>0.06766547399433856</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3362,22 +3102,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3498,11 +3228,6 @@
       <c r="R20" t="n">
         <v>0.07099656203622912</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3515,22 +3240,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3648,11 +3363,6 @@
       <c r="R21" t="n">
         <v>0.1660879816224674</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3665,22 +3375,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3801,11 +3501,6 @@
       <c r="R22" t="n">
         <v>0.1698846305866911</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3818,22 +3513,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3951,11 +3636,6 @@
       <c r="R23" t="n">
         <v>0.3239740876092573</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3968,22 +3648,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4104,11 +3774,6 @@
       <c r="R24" t="n">
         <v>0.150121932120724</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4121,22 +3786,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4254,11 +3909,6 @@
       <c r="R25" t="n">
         <v>0.1373814168975964</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4271,22 +3921,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4407,11 +4047,6 @@
       <c r="R26" t="n">
         <v>0.0801980491565122</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4424,22 +4059,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4557,11 +4182,6 @@
       <c r="R27" t="n">
         <v>0.03256822200315795</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4574,22 +4194,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4710,11 +4320,6 @@
       <c r="R28" t="n">
         <v>0.04084022651131074</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4727,22 +4332,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4860,11 +4455,6 @@
       <c r="R29" t="n">
         <v>0.02035513875197372</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4877,22 +4467,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5013,11 +4593,6 @@
       <c r="R30" t="n">
         <v>0.04513919772302766</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5030,22 +4605,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5163,11 +4728,6 @@
       <c r="R31" t="n">
         <v>0.02646168037756584</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5180,22 +4740,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5316,11 +4866,6 @@
       <c r="R32" t="n">
         <v>0.04632512081591509</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5333,22 +4878,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5466,11 +5001,6 @@
       <c r="R33" t="n">
         <v>0.01424859712638161</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5483,22 +5013,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5619,11 +5139,6 @@
       <c r="R34" t="n">
         <v>0.06559637107533577</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5636,22 +5151,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5769,11 +5274,6 @@
       <c r="R35" t="n">
         <v>0.0223906526271711</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5786,22 +5286,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5922,11 +5412,6 @@
       <c r="R36" t="n">
         <v>0.0684129384209434</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5939,22 +5424,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6072,11 +5547,6 @@
       <c r="R37" t="n">
         <v>0.03460373587835533</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6089,22 +5559,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6225,11 +5685,6 @@
       <c r="R38" t="n">
         <v>0.04966052951466098</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6242,22 +5697,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6375,11 +5820,6 @@
       <c r="R39" t="n">
         <v>0.03256822200315795</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6392,22 +5832,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6528,11 +5958,6 @@
       <c r="R40" t="n">
         <v>0.03142696196151679</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6545,22 +5970,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6678,11 +6093,6 @@
       <c r="R41" t="n">
         <v>0.02646168037756584</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6695,22 +6105,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6831,11 +6231,6 @@
       <c r="R42" t="n">
         <v>0.02786919268285451</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6848,22 +6243,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6981,11 +6366,6 @@
       <c r="R43" t="n">
         <v>0.07124298563190803</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6998,22 +6378,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7134,11 +6504,6 @@
       <c r="R44" t="n">
         <v>0.07108126537994011</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7151,22 +6516,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7284,11 +6639,6 @@
       <c r="R45" t="n">
         <v>0.1669121377661845</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7301,22 +6651,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7437,11 +6777,6 @@
       <c r="R46" t="n">
         <v>0.1681045984167926</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7454,22 +6789,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7587,11 +6912,6 @@
       <c r="R47" t="n">
         <v>0.1954093320189478</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7604,22 +6924,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7740,11 +7050,6 @@
       <c r="R48" t="n">
         <v>0.1446084971389605</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7757,22 +7062,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7890,11 +7185,6 @@
       <c r="R49" t="n">
         <v>0.1099177492606581</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7907,22 +7197,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8043,11 +7323,6 @@
       <c r="R50" t="n">
         <v>0.08203234207854505</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8060,22 +7335,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8193,11 +7458,6 @@
       <c r="R51" t="n">
         <v>0.0564520914940418</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8210,22 +7470,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8346,11 +7596,6 @@
       <c r="R52" t="n">
         <v>0.05628227954267889</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8363,22 +7608,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8496,11 +7731,6 @@
       <c r="R53" t="n">
         <v>0.0282260457470209</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8513,22 +7743,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8649,11 +7869,6 @@
       <c r="R54" t="n">
         <v>0.05834228454554818</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8666,22 +7881,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8799,11 +8004,6 @@
       <c r="R55" t="n">
         <v>0.01612916899829766</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8816,22 +8016,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8952,11 +8142,6 @@
       <c r="R56" t="n">
         <v>0.05687085240064155</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8969,22 +8154,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9102,11 +8277,6 @@
       <c r="R57" t="n">
         <v>0.01209687674872324</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9119,22 +8289,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9255,11 +8415,6 @@
       <c r="R58" t="n">
         <v>0.06967231206132929</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9272,22 +8427,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9405,11 +8550,6 @@
       <c r="R59" t="n">
         <v>0.03024219187180811</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9422,22 +8562,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9558,11 +8688,6 @@
       <c r="R60" t="n">
         <v>0.07680875796412649</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9575,22 +8700,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9708,11 +8823,6 @@
       <c r="R61" t="n">
         <v>0.03629063024616973</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9725,22 +8835,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9861,11 +8961,6 @@
       <c r="R62" t="n">
         <v>0.05628227954267889</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9878,22 +8973,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10011,11 +9096,6 @@
       <c r="R63" t="n">
         <v>0.03225833799659531</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10028,22 +9108,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10164,11 +9234,6 @@
       <c r="R64" t="n">
         <v>0.03288650843866335</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10181,22 +9246,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10314,11 +9369,6 @@
       <c r="R65" t="n">
         <v>0.03225833799659531</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10331,22 +9381,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10467,11 +9507,6 @@
       <c r="R66" t="n">
         <v>0.02906078486190609</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10484,22 +9519,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10617,11 +9642,6 @@
       <c r="R67" t="n">
         <v>0.03427448412138252</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10634,22 +9654,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11256,11 +10266,6 @@
       <c r="R71" t="n">
         <v>0.09534880298995012</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11273,22 +10278,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11406,11 +10401,6 @@
       <c r="R72" t="n">
         <v>0.2036307586035079</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11423,22 +10413,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -12207,11 +11187,6 @@
       <c r="R77" t="n">
         <v>0.2207148217359956</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12224,22 +11199,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12357,11 +11322,6 @@
       <c r="R78" t="n">
         <v>0.1895177357299975</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12374,22 +11334,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13320,11 +12270,6 @@
       <c r="R84" t="n">
         <v>0.1896676034784656</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13337,22 +12282,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13470,11 +12405,6 @@
       <c r="R85" t="n">
         <v>0.06250052986840342</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13487,22 +12417,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14271,11 +13191,6 @@
       <c r="R90" t="n">
         <v>0.1051007123736524</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14288,22 +13203,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14421,11 +13326,6 @@
       <c r="R91" t="n">
         <v>0.03994314931501144</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14438,22 +13338,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15222,11 +14112,6 @@
       <c r="R96" t="n">
         <v>0.06202185392683176</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15239,22 +14124,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15534,11 +14409,6 @@
       <c r="R98" t="n">
         <v>0.02196873212325629</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15551,22 +14421,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -16173,11 +15033,6 @@
       <c r="R102" t="n">
         <v>0.07299270072992702</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16190,22 +15045,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16485,11 +15330,6 @@
       <c r="R104" t="n">
         <v>0.02995736198625858</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16502,22 +15342,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -17286,11 +16116,6 @@
       <c r="R109" t="n">
         <v>0.07906323596097303</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17303,22 +16128,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17436,11 +16251,6 @@
       <c r="R110" t="n">
         <v>0.009985787328752859</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17453,22 +16263,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -18237,11 +17037,6 @@
       <c r="R115" t="n">
         <v>0.09639717390986352</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18254,22 +17049,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18387,11 +17172,6 @@
       <c r="R116" t="n">
         <v>0.03395167691775972</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18404,22 +17184,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -19350,11 +18120,6 @@
       <c r="R122" t="n">
         <v>0.09215511314600003</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19367,22 +18132,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19500,11 +18255,6 @@
       <c r="R123" t="n">
         <v>0.04393746424651258</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19517,22 +18267,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -20301,11 +19041,6 @@
       <c r="R128" t="n">
         <v>0.07482117519710955</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20318,22 +19053,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20451,11 +19176,6 @@
       <c r="R129" t="n">
         <v>0.04593462171226315</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20468,22 +19188,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -21252,11 +19962,6 @@
       <c r="R134" t="n">
         <v>0.04329827538288256</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21269,22 +19974,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -21402,11 +20097,6 @@
       <c r="R135" t="n">
         <v>0.05791756650676659</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21419,22 +20109,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -22365,11 +21045,6 @@
       <c r="R141" t="n">
         <v>0.07482117519710955</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22382,22 +21057,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22515,11 +21180,6 @@
       <c r="R142" t="n">
         <v>0.05791756650676659</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22532,22 +21192,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -23316,11 +21966,6 @@
       <c r="R147" t="n">
         <v>0.08308587978877463</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23333,22 +21978,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -23466,11 +22101,6 @@
       <c r="R148" t="n">
         <v>0.2995736198625857</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23483,22 +22113,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -24267,11 +22887,6 @@
       <c r="R153" t="n">
         <v>0.1324546904027032</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24284,22 +22899,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -24579,11 +23184,6 @@
       <c r="R155" t="n">
         <v>0.307562249725588</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24596,22 +23196,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -25380,11 +23970,6 @@
       <c r="R160" t="n">
         <v>0.1131460000292556</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25397,22 +23982,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25530,11 +24105,6 @@
       <c r="R161" t="n">
         <v>0.1038521882190298</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25547,22 +24117,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -26331,11 +24891,6 @@
       <c r="R166" t="n">
         <v>0.07788094096450315</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26348,22 +24903,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -26481,11 +25026,6 @@
       <c r="R167" t="n">
         <v>0.05342402965959663</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26498,22 +25038,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -27444,11 +25974,6 @@
       <c r="R173" t="n">
         <v>0.0636415151911425</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27461,22 +25986,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -27594,11 +26109,6 @@
       <c r="R174" t="n">
         <v>0.01582934212136197</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27611,22 +26121,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -28395,11 +26895,6 @@
       <c r="R179" t="n">
         <v>0.07323133254871192</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28412,22 +26907,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -28545,11 +27030,6 @@
       <c r="R180" t="n">
         <v>0.01780800988653221</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28562,22 +27042,12 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -29346,11 +27816,6 @@
       <c r="R185" t="n">
         <v>0.07323133254871192</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29363,22 +27828,12 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -29496,11 +27951,6 @@
       <c r="R186" t="n">
         <v>0.005936003295510736</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29513,22 +27963,12 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -30297,11 +28737,6 @@
       <c r="R191" t="n">
         <v>0.08035104543539223</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30314,22 +28749,12 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -30447,11 +28872,6 @@
       <c r="R192" t="n">
         <v>0.01582934212136197</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30464,22 +28884,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -31410,11 +29820,6 @@
       <c r="R198" t="n">
         <v>0.07955189398892812</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31427,22 +29832,12 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -31560,11 +29955,6 @@
       <c r="R199" t="n">
         <v>0.02968001647755368</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31577,22 +29967,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -32361,11 +30741,6 @@
       <c r="R204" t="n">
         <v>0.06073550993127297</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32378,22 +30753,12 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -32511,11 +30876,6 @@
       <c r="R205" t="n">
         <v>0.01780800988653221</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32528,22 +30888,12 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -33312,11 +31662,6 @@
       <c r="R210" t="n">
         <v>0.03930372113973526</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33329,22 +31674,12 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -33624,11 +31959,6 @@
       <c r="R212" t="n">
         <v>0.02572268094721319</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33641,22 +31971,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -34425,11 +32745,6 @@
       <c r="R217" t="n">
         <v>0.03952167153422548</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34442,22 +32757,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -34575,11 +32880,6 @@
       <c r="R218" t="n">
         <v>0.06331736848544786</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34592,22 +32892,12 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -35376,11 +33666,6 @@
       <c r="R223" t="n">
         <v>0.06611161966203159</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35393,22 +33678,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -35526,11 +33801,6 @@
       <c r="R224" t="n">
         <v>0.1187200659102147</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35543,22 +33813,12 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
-      </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -36489,11 +34749,6 @@
       <c r="R230" t="n">
         <v>0.1267018293303111</v>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36506,22 +34761,12 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
-      </c>
-      <c r="AU230" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
@@ -36639,11 +34884,6 @@
       <c r="R231" t="n">
         <v>0.1622507567439601</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36656,22 +34896,12 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
         <v>0</v>
-      </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -37440,11 +35670,6 @@
       <c r="R236" t="n">
         <v>0.1056332911962571</v>
       </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37457,22 +35682,12 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
-      </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
@@ -37590,11 +35805,6 @@
       <c r="R237" t="n">
         <v>0.1543360856832791</v>
       </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37607,22 +35817,12 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
-      </c>
-      <c r="AU237" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>

--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -9774,17 +9774,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -9792,7 +9790,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9802,12 +9800,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -9817,11 +9810,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -9936,17 +9924,15 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -9954,7 +9940,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9964,12 +9950,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -9979,11 +9960,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10098,17 +10074,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -10116,7 +10090,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10126,12 +10100,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -10141,11 +10110,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10533,17 +10497,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -10551,7 +10513,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -10561,12 +10523,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -10576,11 +10533,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10695,17 +10647,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -10713,7 +10663,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -10723,12 +10673,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -10738,11 +10683,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10857,17 +10797,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -10875,7 +10813,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -10885,12 +10823,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -10900,11 +10833,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11019,17 +10947,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -11037,7 +10963,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11047,12 +10973,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -11062,11 +10983,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11454,17 +11370,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -11472,7 +11386,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -11482,12 +11396,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -11497,11 +11406,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11616,17 +11520,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -11634,7 +11536,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -11644,12 +11546,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -11659,11 +11556,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11778,17 +11670,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -11796,7 +11686,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -11806,12 +11696,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -11821,11 +11706,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11940,17 +11820,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -11958,7 +11836,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -11968,12 +11846,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -11983,11 +11856,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12102,17 +11970,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -12120,7 +11986,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12130,12 +11996,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -12145,11 +12006,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12537,17 +12393,15 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -12555,7 +12409,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -12565,12 +12419,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -12580,11 +12429,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12699,17 +12543,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -12717,7 +12559,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -12727,12 +12569,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -12742,11 +12579,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12861,17 +12693,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -12879,7 +12709,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -12889,12 +12719,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -12904,11 +12729,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13023,17 +12843,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -13041,7 +12859,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13051,12 +12869,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -13066,11 +12879,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13458,17 +13266,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -13476,7 +13282,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -13486,12 +13292,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -13501,11 +13302,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13620,17 +13416,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -13638,7 +13432,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -13648,12 +13442,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -13663,11 +13452,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13782,17 +13566,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -13800,7 +13582,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -13810,12 +13592,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -13825,11 +13602,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13944,17 +13716,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -13962,7 +13732,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -13972,12 +13742,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -13987,11 +13752,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14244,17 +14004,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -14262,7 +14020,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -14272,12 +14030,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -14287,11 +14040,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14541,17 +14289,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -14559,7 +14305,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -14569,12 +14315,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -14584,11 +14325,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14703,17 +14439,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -14721,7 +14455,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -14731,12 +14465,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -14746,11 +14475,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14865,17 +14589,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -14883,7 +14605,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -14893,12 +14615,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -14908,11 +14625,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15165,17 +14877,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -15183,7 +14893,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -15193,12 +14903,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -15208,11 +14913,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15462,17 +15162,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -15480,7 +15178,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -15490,12 +15188,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -15505,11 +15198,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15624,17 +15312,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -15642,7 +15328,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -15652,12 +15338,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -15667,11 +15348,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15786,17 +15462,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -15804,7 +15478,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -15814,12 +15488,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -15829,11 +15498,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15948,17 +15612,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -15966,7 +15628,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -15976,12 +15638,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -15991,11 +15648,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16383,17 +16035,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -16401,7 +16051,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -16411,12 +16061,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -16426,11 +16071,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16545,17 +16185,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -16563,7 +16201,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -16573,12 +16211,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -16588,11 +16221,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16707,17 +16335,15 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -16725,7 +16351,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -16735,12 +16361,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -16750,11 +16371,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16869,17 +16485,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -16887,7 +16501,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -16897,12 +16511,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -16912,11 +16521,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17304,17 +16908,15 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -17322,7 +16924,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -17332,12 +16934,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -17347,11 +16944,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17466,17 +17058,15 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -17484,7 +17074,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -17494,12 +17084,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -17509,11 +17094,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17628,17 +17208,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -17646,7 +17224,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -17656,12 +17234,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -17671,11 +17244,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17790,17 +17358,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -17808,7 +17374,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -17818,12 +17384,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -17833,11 +17394,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17952,17 +17508,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -17970,7 +17524,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -17980,12 +17534,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -17995,11 +17544,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -18387,17 +17931,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -18405,7 +17947,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -18415,12 +17957,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -18430,11 +17967,6 @@
       </c>
       <c r="AT124" t="n">
         <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18549,17 +18081,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -18567,7 +18097,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -18577,12 +18107,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -18592,11 +18117,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18711,17 +18231,15 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -18729,7 +18247,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -18739,12 +18257,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -18754,11 +18267,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18873,17 +18381,15 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -18891,7 +18397,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -18901,12 +18407,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -18916,11 +18417,6 @@
       </c>
       <c r="AT127" t="n">
         <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19308,17 +18804,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -19326,7 +18820,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -19336,12 +18830,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -19351,11 +18840,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -19470,17 +18954,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -19488,7 +18970,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -19498,12 +18980,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -19513,11 +18990,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19632,17 +19104,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -19650,7 +19120,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -19660,12 +19130,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -19675,11 +19140,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19794,17 +19254,15 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -19812,7 +19270,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -19822,12 +19280,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
@@ -19837,11 +19290,6 @@
       </c>
       <c r="AT133" t="n">
         <v>1</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20229,17 +19677,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -20247,7 +19693,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -20257,12 +19703,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -20272,11 +19713,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -20391,17 +19827,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -20409,7 +19843,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -20419,12 +19853,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -20434,11 +19863,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -20553,17 +19977,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -20571,7 +19993,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -20581,12 +20003,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -20596,11 +20013,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20715,17 +20127,15 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -20733,7 +20143,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -20743,12 +20153,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
@@ -20758,11 +20163,6 @@
       </c>
       <c r="AT139" t="n">
         <v>1</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20877,17 +20277,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -20895,7 +20293,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -20905,12 +20303,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -20920,11 +20313,6 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21312,17 +20700,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -21330,7 +20716,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -21340,12 +20726,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -21355,11 +20736,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -21474,17 +20850,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -21492,7 +20866,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -21502,12 +20876,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
@@ -21517,11 +20886,6 @@
       </c>
       <c r="AT144" t="n">
         <v>1</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -21636,17 +21000,15 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -21654,7 +21016,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -21664,12 +21026,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -21679,11 +21036,6 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21798,17 +21150,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -21816,7 +21166,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -21826,12 +21176,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -21841,11 +21186,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22233,17 +21573,15 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -22251,7 +21589,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -22261,12 +21599,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -22276,11 +21609,6 @@
       </c>
       <c r="AT149" t="n">
         <v>1</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -22395,17 +21723,15 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -22413,7 +21739,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -22423,12 +21749,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
@@ -22438,11 +21759,6 @@
       </c>
       <c r="AT150" t="n">
         <v>1</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -22557,17 +21873,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -22575,7 +21889,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -22585,12 +21899,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -22600,11 +21909,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22719,17 +22023,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -22737,7 +22039,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -22747,12 +22049,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -22762,11 +22059,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23019,17 +22311,15 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -23037,7 +22327,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -23047,12 +22337,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -23062,11 +22347,6 @@
       </c>
       <c r="AT154" t="n">
         <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -23316,17 +22596,15 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -23334,7 +22612,7 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -23344,12 +22622,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
@@ -23359,11 +22632,6 @@
       </c>
       <c r="AT156" t="n">
         <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -23478,17 +22746,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -23496,7 +22762,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -23506,12 +22772,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -23521,11 +22782,6 @@
       </c>
       <c r="AT157" t="n">
         <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -23640,17 +22896,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -23658,7 +22912,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -23668,12 +22922,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -23683,11 +22932,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -23802,17 +23046,15 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -23820,7 +23062,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -23830,12 +23072,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -23845,11 +23082,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24237,17 +23469,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -24255,7 +23485,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -24265,12 +23495,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -24280,11 +23505,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -24399,17 +23619,15 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -24417,7 +23635,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -24427,12 +23645,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -24442,11 +23655,6 @@
       </c>
       <c r="AT163" t="n">
         <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -24561,17 +23769,15 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -24579,7 +23785,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -24589,12 +23795,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -24604,11 +23805,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -24723,17 +23919,15 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -24741,7 +23935,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -24751,12 +23945,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -24766,11 +23955,6 @@
       </c>
       <c r="AT165" t="n">
         <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -25158,17 +24342,15 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -25176,7 +24358,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -25186,12 +24368,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -25201,11 +24378,6 @@
       </c>
       <c r="AT168" t="n">
         <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -25320,17 +24492,15 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -25338,7 +24508,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -25348,12 +24518,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -25363,11 +24528,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -25482,17 +24642,15 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -25500,7 +24658,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -25510,12 +24668,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -25525,11 +24678,6 @@
       </c>
       <c r="AT170" t="n">
         <v>1</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -25644,17 +24792,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -25662,7 +24808,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -25672,12 +24818,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -25687,11 +24828,6 @@
       </c>
       <c r="AT171" t="n">
         <v>1</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -25806,17 +24942,15 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -25824,7 +24958,7 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -25834,12 +24968,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
@@ -25849,11 +24978,6 @@
       </c>
       <c r="AT172" t="n">
         <v>1</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -26241,17 +25365,15 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -26259,7 +25381,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -26269,12 +25391,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -26284,11 +25401,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -26403,17 +25515,15 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -26421,7 +25531,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -26431,12 +25541,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -26446,11 +25551,6 @@
       </c>
       <c r="AT176" t="n">
         <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -26565,17 +25665,15 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -26583,7 +25681,7 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -26593,12 +25691,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
@@ -26608,11 +25701,6 @@
       </c>
       <c r="AT177" t="n">
         <v>1</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -26727,17 +25815,15 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -26745,7 +25831,7 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -26755,12 +25841,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
@@ -26770,11 +25851,6 @@
       </c>
       <c r="AT178" t="n">
         <v>1</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -27162,17 +26238,15 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -27180,7 +26254,7 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -27190,12 +26264,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
@@ -27205,11 +26274,6 @@
       </c>
       <c r="AT181" t="n">
         <v>1</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -27324,17 +26388,15 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -27342,7 +26404,7 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -27352,12 +26414,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
@@ -27367,11 +26424,6 @@
       </c>
       <c r="AT182" t="n">
         <v>1</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -27486,17 +26538,15 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -27504,7 +26554,7 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -27514,12 +26564,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
@@ -27529,11 +26574,6 @@
       </c>
       <c r="AT183" t="n">
         <v>1</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -27648,17 +26688,15 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -27666,7 +26704,7 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -27676,12 +26714,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
@@ -27691,11 +26724,6 @@
       </c>
       <c r="AT184" t="n">
         <v>1</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -28083,17 +27111,15 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
       <c r="Q187" t="n">
         <v>0</v>
       </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U187" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -28101,7 +27127,7 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -28111,12 +27137,7 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
@@ -28126,11 +27147,6 @@
       </c>
       <c r="AT187" t="n">
         <v>1</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -28245,17 +27261,15 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
       <c r="Q188" t="n">
         <v>0</v>
       </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -28263,7 +27277,7 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -28273,12 +27287,7 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
@@ -28288,11 +27297,6 @@
       </c>
       <c r="AT188" t="n">
         <v>1</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -28407,17 +27411,15 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
       <c r="Q189" t="n">
         <v>0</v>
       </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -28425,7 +27427,7 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -28435,12 +27437,7 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
@@ -28450,11 +27447,6 @@
       </c>
       <c r="AT189" t="n">
         <v>1</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -28569,17 +27561,15 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -28587,7 +27577,7 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -28597,12 +27587,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
@@ -28612,11 +27597,6 @@
       </c>
       <c r="AT190" t="n">
         <v>1</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -29004,17 +27984,15 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
       <c r="Q193" t="n">
         <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -29022,7 +28000,7 @@
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -29032,12 +28010,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
@@ -29047,11 +28020,6 @@
       </c>
       <c r="AT193" t="n">
         <v>1</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -29166,17 +28134,15 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
       <c r="Q194" t="n">
         <v>0</v>
       </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -29184,7 +28150,7 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -29194,12 +28160,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
@@ -29209,11 +28170,6 @@
       </c>
       <c r="AT194" t="n">
         <v>1</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -29328,17 +28284,15 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -29346,7 +28300,7 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -29356,12 +28310,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
@@ -29371,11 +28320,6 @@
       </c>
       <c r="AT195" t="n">
         <v>1</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -29490,17 +28434,15 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -29508,7 +28450,7 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -29518,12 +28460,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
@@ -29533,11 +28470,6 @@
       </c>
       <c r="AT196" t="n">
         <v>1</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -29652,17 +28584,15 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -29670,7 +28600,7 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -29680,12 +28610,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
@@ -29695,11 +28620,6 @@
       </c>
       <c r="AT197" t="n">
         <v>1</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -30087,17 +29007,15 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -30105,7 +29023,7 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -30115,12 +29033,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
@@ -30130,11 +29043,6 @@
       </c>
       <c r="AT200" t="n">
         <v>1</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -30249,17 +29157,15 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -30267,7 +29173,7 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -30277,12 +29183,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
@@ -30292,11 +29193,6 @@
       </c>
       <c r="AT201" t="n">
         <v>1</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -30411,17 +29307,15 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
       <c r="Q202" t="n">
         <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -30429,7 +29323,7 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -30439,12 +29333,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
@@ -30454,11 +29343,6 @@
       </c>
       <c r="AT202" t="n">
         <v>1</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -30573,17 +29457,15 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -30591,7 +29473,7 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -30601,12 +29483,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
@@ -30616,11 +29493,6 @@
       </c>
       <c r="AT203" t="n">
         <v>1</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -31008,17 +29880,15 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -31026,7 +29896,7 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -31036,12 +29906,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
@@ -31051,11 +29916,6 @@
       </c>
       <c r="AT206" t="n">
         <v>1</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -31170,17 +30030,15 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
       <c r="Q207" t="n">
         <v>0</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -31188,7 +30046,7 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -31198,12 +30056,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
@@ -31213,11 +30066,6 @@
       </c>
       <c r="AT207" t="n">
         <v>1</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -31332,17 +30180,15 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
       <c r="Q208" t="n">
         <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U208" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -31350,7 +30196,7 @@
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -31360,12 +30206,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
@@ -31375,11 +30216,6 @@
       </c>
       <c r="AT208" t="n">
         <v>1</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -31494,17 +30330,15 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -31512,7 +30346,7 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -31522,12 +30356,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
@@ -31537,11 +30366,6 @@
       </c>
       <c r="AT209" t="n">
         <v>1</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -31794,17 +30618,15 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -31812,7 +30634,7 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -31822,12 +30644,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
@@ -31837,11 +30654,6 @@
       </c>
       <c r="AT211" t="n">
         <v>1</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -32091,17 +30903,15 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
       <c r="Q213" t="n">
         <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U213" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -32109,7 +30919,7 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -32119,12 +30929,7 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
@@ -32134,11 +30939,6 @@
       </c>
       <c r="AT213" t="n">
         <v>1</v>
-      </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
@@ -32253,17 +31053,15 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
       <c r="Q214" t="n">
         <v>0</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U214" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -32271,7 +31069,7 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -32281,12 +31079,7 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
@@ -32296,11 +31089,6 @@
       </c>
       <c r="AT214" t="n">
         <v>1</v>
-      </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -32415,17 +31203,15 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
       <c r="Q215" t="n">
         <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U215" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -32433,7 +31219,7 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -32443,12 +31229,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
@@ -32458,11 +31239,6 @@
       </c>
       <c r="AT215" t="n">
         <v>1</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -32577,17 +31353,15 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
       <c r="Q216" t="n">
         <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -32595,7 +31369,7 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -32605,12 +31379,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
@@ -32620,11 +31389,6 @@
       </c>
       <c r="AT216" t="n">
         <v>1</v>
-      </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -33012,17 +31776,15 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
       <c r="Q219" t="n">
         <v>0</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U219" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -33030,7 +31792,7 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -33040,12 +31802,7 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
@@ -33055,11 +31812,6 @@
       </c>
       <c r="AT219" t="n">
         <v>1</v>
-      </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -33174,17 +31926,15 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U220" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -33192,7 +31942,7 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -33202,12 +31952,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
@@ -33217,11 +31962,6 @@
       </c>
       <c r="AT220" t="n">
         <v>1</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
@@ -33336,17 +32076,15 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -33354,7 +32092,7 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -33364,12 +32102,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
@@ -33379,11 +32112,6 @@
       </c>
       <c r="AT221" t="n">
         <v>1</v>
-      </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -33498,17 +32226,15 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
       <c r="Q222" t="n">
         <v>0</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -33516,7 +32242,7 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -33526,12 +32252,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
@@ -33541,11 +32262,6 @@
       </c>
       <c r="AT222" t="n">
         <v>1</v>
-      </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -33933,17 +32649,15 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -33951,7 +32665,7 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -33961,12 +32675,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
@@ -33976,11 +32685,6 @@
       </c>
       <c r="AT225" t="n">
         <v>1</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -34095,17 +32799,15 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U226" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -34113,7 +32815,7 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -34123,12 +32825,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
@@ -34138,11 +32835,6 @@
       </c>
       <c r="AT226" t="n">
         <v>1</v>
-      </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
@@ -34257,17 +32949,15 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
       <c r="Q227" t="n">
         <v>0</v>
       </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -34275,7 +32965,7 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -34285,12 +32975,7 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
@@ -34300,11 +32985,6 @@
       </c>
       <c r="AT227" t="n">
         <v>1</v>
-      </c>
-      <c r="AU227" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
@@ -34419,17 +33099,15 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U228" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -34437,7 +33115,7 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -34447,12 +33125,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
@@ -34462,11 +33135,6 @@
       </c>
       <c r="AT228" t="n">
         <v>1</v>
-      </c>
-      <c r="AU228" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
@@ -34581,17 +33249,15 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -34599,7 +33265,7 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -34609,12 +33275,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
@@ -34624,11 +33285,6 @@
       </c>
       <c r="AT229" t="n">
         <v>1</v>
-      </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -35016,17 +33672,15 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
       <c r="Q232" t="n">
         <v>0</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U232" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -35034,7 +33688,7 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -35044,12 +33698,7 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
@@ -35059,11 +33708,6 @@
       </c>
       <c r="AT232" t="n">
         <v>1</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -35178,17 +33822,15 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
       <c r="Q233" t="n">
         <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U233" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -35196,7 +33838,7 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -35206,12 +33848,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
@@ -35221,11 +33858,6 @@
       </c>
       <c r="AT233" t="n">
         <v>1</v>
-      </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
@@ -35340,17 +33972,15 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
       <c r="Q234" t="n">
         <v>0</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U234" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -35358,7 +33988,7 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -35368,12 +33998,7 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
@@ -35383,11 +34008,6 @@
       </c>
       <c r="AT234" t="n">
         <v>1</v>
-      </c>
-      <c r="AU234" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
@@ -35502,17 +34122,15 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -35520,7 +34138,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -35530,12 +34148,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
@@ -35545,11 +34158,6 @@
       </c>
       <c r="AT235" t="n">
         <v>1</v>
-      </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
@@ -35937,17 +34545,15 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
       <c r="Q238" t="n">
         <v>0</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U238" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -35955,7 +34561,7 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -35965,12 +34571,7 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
@@ -35980,11 +34581,6 @@
       </c>
       <c r="AT238" t="n">
         <v>1</v>
-      </c>
-      <c r="AU238" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
@@ -36099,17 +34695,15 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
       <c r="Q239" t="n">
         <v>0</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U239" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -36117,7 +34711,7 @@
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -36127,12 +34721,7 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
@@ -36142,11 +34731,6 @@
       </c>
       <c r="AT239" t="n">
         <v>1</v>
-      </c>
-      <c r="AU239" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
@@ -36261,17 +34845,15 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
       <c r="Q240" t="n">
         <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U240" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -36279,7 +34861,7 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -36289,12 +34871,7 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
@@ -36304,11 +34881,6 @@
       </c>
       <c r="AT240" t="n">
         <v>1</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
@@ -36423,17 +34995,15 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
       <c r="Q241" t="n">
         <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>HOLD_JP_bc2ab2c1322c24117d1aaa60242f</t>
@@ -36441,7 +35011,7 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -36451,12 +35021,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
@@ -36466,11 +35031,6 @@
       </c>
       <c r="AT241" t="n">
         <v>1</v>
-      </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>

--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -906,6 +906,11 @@
       <c r="R3" t="n">
         <v>0.0328075025427096</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +923,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1179,6 +1194,11 @@
       <c r="R5" t="n">
         <v>0.02255515799811285</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1191,12 +1211,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1452,6 +1482,11 @@
       <c r="R7" t="n">
         <v>0.0205046890891935</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1464,12 +1499,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1725,6 +1770,11 @@
       <c r="R9" t="n">
         <v>0.03075703363379025</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1737,12 +1787,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1998,6 +2058,11 @@
       <c r="R11" t="n">
         <v>0.0328075025427096</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2010,12 +2075,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2271,6 +2346,11 @@
       <c r="R13" t="n">
         <v>0.0451103159962257</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2283,12 +2363,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2544,6 +2634,11 @@
       <c r="R15" t="n">
         <v>0.0492112538140644</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2556,12 +2651,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2817,6 +2922,11 @@
       <c r="R17" t="n">
         <v>0.041009378178387</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2829,12 +2939,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3090,6 +3210,11 @@
       <c r="R19" t="n">
         <v>0.06766547399433856</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3102,12 +3227,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3363,6 +3498,11 @@
       <c r="R21" t="n">
         <v>0.1660879816224674</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3375,12 +3515,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3636,6 +3786,11 @@
       <c r="R23" t="n">
         <v>0.3239740876092573</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3648,12 +3803,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3909,6 +4074,11 @@
       <c r="R25" t="n">
         <v>0.1373814168975964</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3921,12 +4091,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4182,6 +4362,11 @@
       <c r="R27" t="n">
         <v>0.03256822200315795</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4194,12 +4379,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4455,6 +4650,11 @@
       <c r="R29" t="n">
         <v>0.02035513875197372</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4467,12 +4667,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4728,6 +4938,11 @@
       <c r="R31" t="n">
         <v>0.02646168037756584</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4740,12 +4955,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5001,6 +5226,11 @@
       <c r="R33" t="n">
         <v>0.01424859712638161</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5013,12 +5243,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5274,6 +5514,11 @@
       <c r="R35" t="n">
         <v>0.0223906526271711</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5286,12 +5531,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5547,6 +5802,11 @@
       <c r="R37" t="n">
         <v>0.03460373587835533</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5559,12 +5819,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5820,6 +6090,11 @@
       <c r="R39" t="n">
         <v>0.03256822200315795</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5832,12 +6107,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6093,6 +6378,11 @@
       <c r="R41" t="n">
         <v>0.02646168037756584</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6105,12 +6395,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6366,6 +6666,11 @@
       <c r="R43" t="n">
         <v>0.07124298563190803</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6378,12 +6683,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6639,6 +6954,11 @@
       <c r="R45" t="n">
         <v>0.1669121377661845</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6651,12 +6971,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6912,6 +7242,11 @@
       <c r="R47" t="n">
         <v>0.1954093320189478</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6924,12 +7259,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7185,6 +7530,11 @@
       <c r="R49" t="n">
         <v>0.1099177492606581</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7197,12 +7547,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7458,6 +7818,11 @@
       <c r="R51" t="n">
         <v>0.0564520914940418</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7470,12 +7835,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7731,6 +8106,11 @@
       <c r="R53" t="n">
         <v>0.0282260457470209</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7743,12 +8123,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8004,6 +8394,11 @@
       <c r="R55" t="n">
         <v>0.01612916899829766</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8016,12 +8411,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8277,6 +8682,11 @@
       <c r="R57" t="n">
         <v>0.01209687674872324</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8289,12 +8699,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8550,6 +8970,11 @@
       <c r="R59" t="n">
         <v>0.03024219187180811</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8562,12 +8987,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8823,6 +9258,11 @@
       <c r="R61" t="n">
         <v>0.03629063024616973</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8835,12 +9275,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9096,6 +9546,11 @@
       <c r="R63" t="n">
         <v>0.03225833799659531</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9108,12 +9563,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9369,6 +9834,11 @@
       <c r="R65" t="n">
         <v>0.03225833799659531</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9381,12 +9851,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9642,6 +10122,11 @@
       <c r="R67" t="n">
         <v>0.03427448412138252</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9654,12 +10139,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10365,6 +10860,11 @@
       <c r="R72" t="n">
         <v>0.2036307586035079</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10377,12 +10877,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11238,6 +11748,11 @@
       <c r="R78" t="n">
         <v>0.1895177357299975</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11250,12 +11765,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12261,6 +12786,11 @@
       <c r="R85" t="n">
         <v>0.06250052986840342</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12273,12 +12803,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13134,6 +13674,11 @@
       <c r="R91" t="n">
         <v>0.03994314931501144</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13146,12 +13691,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14157,6 +14712,11 @@
       <c r="R98" t="n">
         <v>0.02196873212325629</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14169,12 +14729,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15030,6 +15600,11 @@
       <c r="R104" t="n">
         <v>0.02995736198625858</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15042,12 +15617,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15903,6 +16488,11 @@
       <c r="R110" t="n">
         <v>0.009985787328752859</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15915,12 +16505,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16776,6 +17376,11 @@
       <c r="R116" t="n">
         <v>0.03395167691775972</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16788,12 +17393,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17799,6 +18414,11 @@
       <c r="R123" t="n">
         <v>0.04393746424651258</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17811,12 +18431,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18672,6 +19302,11 @@
       <c r="R129" t="n">
         <v>0.04593462171226315</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18684,12 +19319,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -19545,6 +20190,11 @@
       <c r="R135" t="n">
         <v>0.05791756650676659</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19557,12 +20207,22 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -20568,6 +21228,11 @@
       <c r="R142" t="n">
         <v>0.05791756650676659</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20580,12 +21245,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -21441,6 +22116,11 @@
       <c r="R148" t="n">
         <v>0.2995736198625857</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21453,12 +22133,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -22464,6 +23154,11 @@
       <c r="R155" t="n">
         <v>0.307562249725588</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22476,12 +23171,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -23337,6 +24042,11 @@
       <c r="R161" t="n">
         <v>0.1038521882190298</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23349,12 +24059,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -24210,6 +24930,11 @@
       <c r="R167" t="n">
         <v>0.05342402965959663</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24222,12 +24947,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -25233,6 +25968,11 @@
       <c r="R174" t="n">
         <v>0.01582934212136197</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25245,12 +25985,22 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -26106,6 +26856,11 @@
       <c r="R180" t="n">
         <v>0.01780800988653221</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26118,12 +26873,22 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -26979,6 +27744,11 @@
       <c r="R186" t="n">
         <v>0.005936003295510736</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26991,12 +27761,22 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -27852,6 +28632,11 @@
       <c r="R192" t="n">
         <v>0.01582934212136197</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27864,12 +28649,22 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -28875,6 +29670,11 @@
       <c r="R199" t="n">
         <v>0.02968001647755368</v>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28887,12 +29687,22 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -29748,6 +30558,11 @@
       <c r="R205" t="n">
         <v>0.01780800988653221</v>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29760,12 +30575,22 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -30771,6 +31596,11 @@
       <c r="R212" t="n">
         <v>0.02572268094721319</v>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30783,12 +31613,22 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -31644,6 +32484,11 @@
       <c r="R218" t="n">
         <v>0.06331736848544786</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31656,12 +32501,22 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -32517,6 +33372,11 @@
       <c r="R224" t="n">
         <v>0.1187200659102147</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32529,12 +33389,22 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -33540,6 +34410,11 @@
       <c r="R231" t="n">
         <v>0.1622507567439601</v>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33552,12 +34427,22 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
         <v>0</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -34413,6 +35298,11 @@
       <c r="R237" t="n">
         <v>0.1543360856832791</v>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34425,12 +35315,22 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
